--- a/docagent_clean_mvp/sample_data/raw_excels/CAIQ_SetA.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/CAIQ_SetA.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Multi-factor authentication (MFA) is enforced for all privileged and remote access accounts.</t>
+          <t>Standard Identity &amp; Access Management control mandates that multi-factor authentication (MFA) is enforced for all privileged and remote access accounts. [CAIQ-034]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Compliant - evidence on file (MFA enforcement logs)</t>
+          <t>Compliant - evidence on file</t>
         </is>
       </c>
     </row>
